--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_41.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3232739.085308719</v>
+        <v>3269097.131615935</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337385</v>
+        <v>13275569.19337386</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337385</v>
+        <v>13275569.19337386</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117060952</v>
+        <v>603.5370117102204</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117060952</v>
+        <v>603.5370117102204</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
@@ -742,16 +742,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>170.4651902778821</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
         <v>209.5726123064429</v>
@@ -781,13 +781,13 @@
         <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
-        <v>278.6487531723255</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>374</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
         <v>0.1959257979225981</v>
@@ -912,7 +912,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T5" t="n">
         <v>184.8805867536895</v>
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>313.6694368612783</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>128.9709564352694</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>133.6519859716245</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1207,19 +1207,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>128.9709564352694</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>91.44348000027222</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4605873653141466</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>3.999611346725456</v>
+        <v>177.5914272286986</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1495,13 +1495,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1510,10 +1510,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>251.9832086481073</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1565,16 +1565,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,13 +1617,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H14" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>142.3350019731772</v>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>26.93768689770263</v>
@@ -1693,13 +1693,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>192.2280582198497</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1732,16 +1732,16 @@
         <v>180.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797057</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T15" t="n">
-        <v>81.3753501231742</v>
+        <v>254.9671660051471</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V15" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
         <v>111.3731429098285</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
@@ -1802,16 +1802,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S16" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H17" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>116.6353649945383</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H18" t="n">
-        <v>177.613789860847</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1963,25 +1963,25 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R18" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S18" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T18" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>98.86273944538755</v>
@@ -2039,13 +2039,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P19" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q19" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S19" t="n">
         <v>30.56285675203577</v>
@@ -2091,7 +2091,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H20" t="n">
         <v>72.84688483418068</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S20" t="n">
         <v>142.3350019731772</v>
@@ -2139,7 +2139,7 @@
         <v>308.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>317.8340633462618</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X20" t="n">
         <v>271.2818334606677</v>
@@ -2158,7 +2158,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>135.063180218145</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -2170,10 +2170,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>3.999611346725456</v>
+        <v>98.96287911935113</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V21" t="n">
         <v>93.51066719152016</v>
@@ -2276,13 +2276,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q22" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
         <v>30.56285675203577</v>
@@ -2331,7 +2331,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C24" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>3.99961134672543</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>180.333570877285</v>
@@ -2452,16 +2452,16 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>173.3546605387601</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2504,13 +2504,13 @@
         <v>10.32179209220538</v>
       </c>
       <c r="M25" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N25" t="n">
         <v>155.2579933044718</v>
       </c>
       <c r="O25" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
         <v>291.4220612627038</v>
@@ -2686,7 +2686,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490372</v>
+        <v>252.7534963968771</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2695,7 +2695,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>272.4545553273608</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>399.3913927661343</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N28" t="n">
         <v>155.2579933044718</v>
@@ -2802,7 +2802,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>135.063180218145</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
         <v>26.93768689770263</v>
@@ -2881,10 +2881,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V30" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>98.86273944538755</v>
+        <v>193.8260072180132</v>
       </c>
       <c r="Y30" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2984,16 +2984,16 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O31" t="n">
-        <v>231.765039488851</v>
+        <v>230.9267936392535</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S31" t="n">
         <v>30.56285675203577</v>
@@ -3039,13 +3039,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H32" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3106,10 +3106,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>135.063180218145</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
         <v>342.6720972219126</v>
@@ -3118,10 +3118,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>3.999611346725456</v>
+        <v>98.96287911935102</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873961</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3154,13 +3154,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
@@ -3212,28 +3212,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M34" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N34" t="n">
-        <v>154.4197474548741</v>
+        <v>155.2579933044718</v>
       </c>
       <c r="O34" t="n">
         <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S34" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3343,10 +3343,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>213.6917283274922</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>21.67209722191262</v>
@@ -3361,7 +3361,7 @@
         <v>4.021973978873973</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
-        <v>180.333570877285</v>
+        <v>404.6459244566755</v>
       </c>
       <c r="S36" t="n">
         <v>131.8202263797057</v>
@@ -3403,10 +3403,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>78.39139276613435</v>
@@ -3470,7 +3470,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090246892</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3586,16 +3586,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>3.999611346725456</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873961</v>
+        <v>177.6137898608469</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T39" t="n">
         <v>81.3753501231742</v>
@@ -3637,16 +3637,16 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>251.9832086481075</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3707,7 +3707,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090247624</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3753,10 +3753,10 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>237.1483725282997</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
@@ -3832,10 +3832,10 @@
         <v>3.999611346725456</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873961</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>173.591815881973</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4054,7 +4054,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>26.93768689770263</v>
@@ -4066,13 +4066,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>306.9628756676119</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
-        <v>191.6509141932353</v>
+        <v>94.96326777262577</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,19 +4096,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4169,16 +4169,16 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O46" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598396</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S46" t="n">
         <v>30.56285675203577</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.731003807232</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C2" t="n">
-        <v>58.7566823496624</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324847</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398721</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755106</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
@@ -4327,13 +4327,13 @@
         <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>327.128108133742</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M2" t="n">
-        <v>697.388108133742</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.648108133742</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="O2" t="n">
         <v>1067.648108133742</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241.6095073802453</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="C3" t="n">
-        <v>241.6095073802453</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="D3" t="n">
-        <v>241.6095073802453</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="E3" t="n">
-        <v>241.6095073802453</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="F3" t="n">
-        <v>241.6095073802453</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="G3" t="n">
-        <v>241.6095073802453</v>
+        <v>578.2064886541781</v>
       </c>
       <c r="H3" t="n">
-        <v>241.6095073802453</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="I3" t="n">
-        <v>29.92</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="J3" t="n">
-        <v>174.3973709300159</v>
+        <v>177.6113405614803</v>
       </c>
       <c r="K3" t="n">
-        <v>398.6635894772295</v>
+        <v>401.8775591086939</v>
       </c>
       <c r="L3" t="n">
-        <v>717.174568996958</v>
+        <v>720.3885386284223</v>
       </c>
       <c r="M3" t="n">
-        <v>858.2892107398172</v>
+        <v>861.5031803712816</v>
       </c>
       <c r="N3" t="n">
-        <v>1048.06018421531</v>
+        <v>1051.274153846774</v>
       </c>
       <c r="O3" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.994549492757</v>
       </c>
       <c r="P3" t="n">
-        <v>1492.786030368536</v>
+        <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1346.247111942856</v>
+        <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>968.469334165078</v>
+        <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>687.0059471223249</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>309.2281693445471</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>309.0302644981606</v>
+        <v>1146.622528526128</v>
       </c>
       <c r="V3" t="n">
-        <v>294.3730249107666</v>
+        <v>1131.965288938734</v>
       </c>
       <c r="W3" t="n">
-        <v>261.6728805574044</v>
+        <v>1099.265144585372</v>
       </c>
       <c r="X3" t="n">
-        <v>241.6095073802453</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="Y3" t="n">
-        <v>241.6095073802453</v>
+        <v>1079.201771408213</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685.2647991644683</v>
+        <v>975.6323100356523</v>
       </c>
       <c r="C4" t="n">
-        <v>811.2668049829041</v>
+        <v>1101.634315854088</v>
       </c>
       <c r="D4" t="n">
-        <v>924.5859491079042</v>
+        <v>1101.634315854088</v>
       </c>
       <c r="E4" t="n">
-        <v>1042.414853319317</v>
+        <v>1101.634315854088</v>
       </c>
       <c r="F4" t="n">
-        <v>1166.775825911253</v>
+        <v>1101.634315854088</v>
       </c>
       <c r="G4" t="n">
-        <v>1320.364486880105</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="H4" t="n">
-        <v>1491.500062859175</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="I4" t="n">
-        <v>1496</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="J4" t="n">
-        <v>1496</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.273682802524</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1258.790761928658</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>1042.177358901337</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>774.2966876474056</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
-        <v>460.7236912579127</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>139.176451535273</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>139.176451535273</v>
+        <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>139.176451535273</v>
+        <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>139.176451535273</v>
+        <v>230.7225695205111</v>
       </c>
       <c r="V4" t="n">
-        <v>139.176451535273</v>
+        <v>429.543962406457</v>
       </c>
       <c r="W4" t="n">
-        <v>311.0673697949504</v>
+        <v>601.4348806661344</v>
       </c>
       <c r="X4" t="n">
-        <v>462.0981608191439</v>
+        <v>752.4656716903279</v>
       </c>
       <c r="Y4" t="n">
-        <v>573.5074614981762</v>
+        <v>863.8749723693602</v>
       </c>
     </row>
     <row r="5">
@@ -4534,40 +4534,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G5" t="n">
-        <v>35.58557518755106</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H5" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K5" t="n">
-        <v>451.8183303517587</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L5" t="n">
+        <v>327.128108133742</v>
+      </c>
+      <c r="M5" t="n">
         <v>697.388108133742</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1067.648108133742</v>
       </c>
       <c r="N5" t="n">
         <v>1067.648108133742</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>698.2100239989707</v>
+        <v>1222.526720202428</v>
       </c>
       <c r="C6" t="n">
-        <v>698.2100239989707</v>
+        <v>857.7793338938229</v>
       </c>
       <c r="D6" t="n">
-        <v>346.7578150113922</v>
+        <v>506.3271249062445</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>160.193693368959</v>
       </c>
       <c r="F6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T6" t="n">
-        <v>1143.60646374105</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U6" t="n">
-        <v>1143.408558894664</v>
+        <v>1289.947477320344</v>
       </c>
       <c r="V6" t="n">
-        <v>1128.75131930727</v>
+        <v>1275.29023773295</v>
       </c>
       <c r="W6" t="n">
-        <v>1096.051174953908</v>
+        <v>1242.590093379587</v>
       </c>
       <c r="X6" t="n">
-        <v>1075.987801776748</v>
+        <v>1222.526720202428</v>
       </c>
       <c r="Y6" t="n">
-        <v>698.2100239989707</v>
+        <v>1222.526720202428</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>579.5287926092951</v>
+        <v>353.8993100962325</v>
       </c>
       <c r="C7" t="n">
-        <v>579.5287926092951</v>
+        <v>479.9013159146683</v>
       </c>
       <c r="D7" t="n">
-        <v>579.5287926092951</v>
+        <v>593.2204600396684</v>
       </c>
       <c r="E7" t="n">
-        <v>579.5287926092951</v>
+        <v>711.0493642510814</v>
       </c>
       <c r="F7" t="n">
-        <v>703.8897652012306</v>
+        <v>835.4103368430169</v>
       </c>
       <c r="G7" t="n">
-        <v>857.4784261700831</v>
+        <v>988.9989978118695</v>
       </c>
       <c r="H7" t="n">
-        <v>1028.614002149153</v>
+        <v>1160.134573790939</v>
       </c>
       <c r="I7" t="n">
-        <v>1255.222976822941</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J7" t="n">
-        <v>1255.222976822941</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K7" t="n">
         <v>1386.743548464727</v>
@@ -4746,22 +4746,22 @@
         <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>134.1462746260461</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="U7" t="n">
-        <v>380.7073997233492</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="V7" t="n">
-        <v>579.5287926092951</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="W7" t="n">
-        <v>579.5287926092951</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="X7" t="n">
-        <v>579.5287926092951</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="Y7" t="n">
-        <v>579.5287926092951</v>
+        <v>242.1419724299404</v>
       </c>
     </row>
     <row r="8">
@@ -4798,22 +4798,22 @@
         <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>451.8183303517587</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>515.8802453266331</v>
+        <v>1140.7</v>
       </c>
       <c r="M8" t="n">
-        <v>697.388108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1222.526720202428</v>
+        <v>394.6673863086054</v>
       </c>
       <c r="C9" t="n">
-        <v>857.7793338938229</v>
+        <v>29.92</v>
       </c>
       <c r="D9" t="n">
-        <v>506.3271249062445</v>
+        <v>29.92</v>
       </c>
       <c r="E9" t="n">
-        <v>160.193693368959</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
         <v>29.92</v>
@@ -4916,10 +4916,10 @@
         <v>1242.590093379587</v>
       </c>
       <c r="X9" t="n">
-        <v>1222.526720202428</v>
+        <v>1150.222941864161</v>
       </c>
       <c r="Y9" t="n">
-        <v>1222.526720202428</v>
+        <v>772.4451640863832</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>259.1973975316665</v>
+        <v>1250.668263144111</v>
       </c>
       <c r="C10" t="n">
-        <v>259.1973975316665</v>
+        <v>1376.670268962547</v>
       </c>
       <c r="D10" t="n">
-        <v>372.5165416566666</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="E10" t="n">
-        <v>490.3454458680797</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="F10" t="n">
-        <v>614.7064184600151</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="G10" t="n">
-        <v>768.2950794288677</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="H10" t="n">
-        <v>939.4306554079374</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I10" t="n">
-        <v>1166.039630081725</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4986,19 +4986,19 @@
         <v>259.1973975316665</v>
       </c>
       <c r="U10" t="n">
-        <v>259.1973975316665</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V10" t="n">
-        <v>259.1973975316665</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W10" t="n">
-        <v>259.1973975316665</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="X10" t="n">
-        <v>259.1973975316665</v>
+        <v>1027.501624798786</v>
       </c>
       <c r="Y10" t="n">
-        <v>259.1973975316665</v>
+        <v>1138.910925477819</v>
       </c>
     </row>
     <row r="11">
@@ -5008,40 +5008,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D11" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E11" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F11" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G11" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H11" t="n">
-        <v>52.38523976294358</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K11" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L11" t="n">
-        <v>991.9887866314309</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="M11" t="n">
-        <v>1595.767892278425</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="N11" t="n">
         <v>2238.277892278425</v>
@@ -5068,16 +5068,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W11" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X11" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>816.9377012410212</v>
+        <v>992.2829698086706</v>
       </c>
       <c r="C12" t="n">
-        <v>452.1903149324157</v>
+        <v>627.5355835000653</v>
       </c>
       <c r="D12" t="n">
-        <v>100.7381059448373</v>
+        <v>600.3257987549111</v>
       </c>
       <c r="E12" t="n">
-        <v>78.84709864997603</v>
+        <v>578.43479146005</v>
       </c>
       <c r="F12" t="n">
-        <v>60.02261143999941</v>
+        <v>235.367880007649</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5141,7 +5141,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T12" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U12" t="n">
         <v>1766.721857646244</v>
@@ -5153,10 +5153,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X12" t="n">
-        <v>1459.907161134389</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y12" t="n">
-        <v>1205.378667550442</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="13">
@@ -5196,25 +5196,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R13" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5245,40 +5245,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C14" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D14" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E14" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F14" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G14" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L14" t="n">
-        <v>1418.446838088717</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="M14" t="n">
-        <v>2060.956838088718</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="N14" t="n">
         <v>2238.277892278425</v>
@@ -5293,28 +5293,28 @@
         <v>2596</v>
       </c>
       <c r="R14" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U14" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X14" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="15">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>992.2829698086705</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C15" t="n">
-        <v>627.5355835000651</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D15" t="n">
-        <v>600.3257987549109</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E15" t="n">
-        <v>254.1923672176254</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F15" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5375,25 +5375,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S15" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095641</v>
+        <v>1347.095458285568</v>
       </c>
       <c r="U15" t="n">
-        <v>1766.721857646244</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V15" t="n">
-        <v>1672.26663826087</v>
+        <v>848.4365212083717</v>
       </c>
       <c r="W15" t="n">
-        <v>1559.768514109528</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X15" t="n">
-        <v>1459.907161134389</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y15" t="n">
-        <v>1380.723936118091</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="16">
@@ -5445,13 +5445,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R16" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C17" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D17" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E17" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F17" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G17" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H17" t="n">
         <v>51.92</v>
@@ -5512,10 +5512,10 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L17" t="n">
-        <v>1418.446838088717</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M17" t="n">
-        <v>2060.956838088718</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N17" t="n">
         <v>2238.277892278425</v>
@@ -5530,28 +5530,28 @@
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X17" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="18">
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>668.0405455662462</v>
+        <v>912.8601939406431</v>
       </c>
       <c r="C18" t="n">
-        <v>627.5355835000652</v>
+        <v>548.1128076320376</v>
       </c>
       <c r="D18" t="n">
-        <v>600.325798754911</v>
+        <v>196.6605986444592</v>
       </c>
       <c r="E18" t="n">
-        <v>578.4347914600498</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F18" t="n">
-        <v>235.3678800076489</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G18" t="n">
-        <v>231.3278685463101</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H18" t="n">
         <v>51.92</v>
@@ -5606,31 +5606,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q18" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R18" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S18" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T18" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U18" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V18" t="n">
-        <v>1348.024214018445</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W18" t="n">
-        <v>911.2836656246791</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X18" t="n">
-        <v>811.4223126495401</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y18" t="n">
-        <v>732.2390876332428</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="19">
@@ -5685,7 +5685,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R19" t="n">
         <v>82.79157247680381</v>
@@ -5731,7 +5731,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F20" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G20" t="n">
         <v>125.5027119537179</v>
@@ -5767,19 +5767,19 @@
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S20" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W20" t="n">
         <v>1225.542801964753</v>
@@ -5801,19 +5801,19 @@
         <v>1237.102618183067</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.675163417264</v>
+        <v>1196.597656116886</v>
       </c>
       <c r="D21" t="n">
-        <v>749.2229544296858</v>
+        <v>845.1454471293077</v>
       </c>
       <c r="E21" t="n">
-        <v>403.0895228924003</v>
+        <v>499.0120155920222</v>
       </c>
       <c r="F21" t="n">
-        <v>60.02261143999941</v>
+        <v>155.9451041396213</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5922,7 +5922,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q22" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R22" t="n">
         <v>82.79157247680381</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D23" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5986,46 +5986,46 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L23" t="n">
-        <v>991.9887866314309</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M23" t="n">
-        <v>1009.32297330616</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N23" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O23" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P23" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.4528527561725</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C24" t="n">
-        <v>127.9478906899915</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D24" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F24" t="n">
         <v>60.0226114399994</v>
@@ -6080,31 +6080,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q24" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R24" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S24" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T24" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U24" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V24" t="n">
-        <v>1268.601438150418</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>831.8608897566517</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>407.7571125390884</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.6513948231691</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="25">
@@ -6147,10 +6147,10 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M25" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N25" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O25" t="n">
         <v>1115.142339091088</v>
@@ -6217,22 +6217,22 @@
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K26" t="n">
-        <v>307.5796384907274</v>
+        <v>989.863031102066</v>
       </c>
       <c r="L26" t="n">
-        <v>523.631587033441</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="M26" t="n">
-        <v>1009.32297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N26" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O26" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P26" t="n">
         <v>2009.555081027735</v>
@@ -6329,13 +6329,13 @@
         <v>1846.683151095642</v>
       </c>
       <c r="U27" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V27" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W27" t="n">
-        <v>1559.768514109528</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X27" t="n">
         <v>1284.561892566739</v>
@@ -6381,7 +6381,7 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
         <v>1506.07469544798</v>
@@ -6442,7 +6442,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G29" t="n">
         <v>125.5027119537179</v>
@@ -6454,13 +6454,13 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K29" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L29" t="n">
-        <v>1149.849898617045</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="M29" t="n">
         <v>1792.359898617045</v>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>264.3753454557945</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C30" t="n">
         <v>127.9478906899915</v>
@@ -6521,10 +6521,10 @@
         <v>78.84709864997603</v>
       </c>
       <c r="F30" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6566,19 +6566,19 @@
         <v>1767.260375227614</v>
       </c>
       <c r="U30" t="n">
-        <v>1687.299081778216</v>
+        <v>1363.056657535792</v>
       </c>
       <c r="V30" t="n">
-        <v>1592.843862392842</v>
+        <v>944.3590139079936</v>
       </c>
       <c r="W30" t="n">
-        <v>1156.103313999076</v>
+        <v>507.6184655142274</v>
       </c>
       <c r="X30" t="n">
-        <v>1056.241961023937</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y30" t="n">
-        <v>652.8163117652153</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="31">
@@ -6627,13 +6627,13 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O31" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P31" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R31" t="n">
         <v>82.79157247680381</v>
@@ -6667,46 +6667,46 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D32" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H32" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I32" t="n">
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K32" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L32" t="n">
-        <v>523.631587033441</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M32" t="n">
-        <v>563.4049796447796</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N32" t="n">
-        <v>1205.91497964478</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O32" t="n">
-        <v>1367.045081027735</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P32" t="n">
         <v>2009.555081027735</v>
@@ -6727,16 +6727,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W32" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="33">
@@ -6749,19 +6749,19 @@
         <v>1237.102618183067</v>
       </c>
       <c r="C33" t="n">
-        <v>1100.675163417264</v>
+        <v>1196.597656116886</v>
       </c>
       <c r="D33" t="n">
-        <v>749.2229544296858</v>
+        <v>1169.387871371732</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0895228924003</v>
+        <v>823.2544398344464</v>
       </c>
       <c r="F33" t="n">
-        <v>60.02261143999941</v>
+        <v>480.1875283820455</v>
       </c>
       <c r="G33" t="n">
-        <v>55.98259997866057</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6861,19 +6861,19 @@
         <v>1505.227982468588</v>
       </c>
       <c r="N34" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O34" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q34" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R34" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6928,25 +6928,25 @@
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L35" t="n">
-        <v>949.6332762537361</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M35" t="n">
-        <v>1114.38799366138</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N35" t="n">
-        <v>1756.89799366138</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O35" t="n">
-        <v>2399.40799366138</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P35" t="n">
-        <v>2596</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>343.7981213238219</v>
+        <v>686.2820590119658</v>
       </c>
       <c r="C36" t="n">
-        <v>127.9478906899915</v>
+        <v>645.7770969457847</v>
       </c>
       <c r="D36" t="n">
-        <v>100.7381059448373</v>
+        <v>294.3248879582063</v>
       </c>
       <c r="E36" t="n">
-        <v>78.84709864997603</v>
+        <v>272.4338806633451</v>
       </c>
       <c r="F36" t="n">
-        <v>60.0226114399994</v>
+        <v>253.6093934533685</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866058</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H36" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I36" t="n">
         <v>51.92</v>
@@ -7028,31 +7028,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R36" t="n">
-        <v>2062.032218270268</v>
+        <v>1756.031307473563</v>
       </c>
       <c r="S36" t="n">
-        <v>1928.880474452383</v>
+        <v>1622.879563655678</v>
       </c>
       <c r="T36" t="n">
-        <v>1846.683151095641</v>
+        <v>1540.682240298936</v>
       </c>
       <c r="U36" t="n">
-        <v>1766.721857646244</v>
+        <v>1460.720946849539</v>
       </c>
       <c r="V36" t="n">
-        <v>1672.26663826087</v>
+        <v>1366.265727464165</v>
       </c>
       <c r="W36" t="n">
-        <v>1235.526089867103</v>
+        <v>1253.767603312823</v>
       </c>
       <c r="X36" t="n">
-        <v>811.4223126495401</v>
+        <v>1153.906250337684</v>
       </c>
       <c r="Y36" t="n">
-        <v>732.2390876332428</v>
+        <v>1074.723025321387</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>686.6440969024278</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C37" t="n">
-        <v>734.4361027208636</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D37" t="n">
-        <v>769.5452468458636</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E37" t="n">
-        <v>809.1641510572766</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F37" t="n">
-        <v>855.3151236492121</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G37" t="n">
-        <v>931.1258141262613</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H37" t="n">
-        <v>1027.892525187298</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I37" t="n">
-        <v>1189.283805434857</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J37" t="n">
-        <v>1515.576154611898</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K37" t="n">
-        <v>1619.080700024176</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L37" t="n">
-        <v>1608.654647405787</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M37" t="n">
-        <v>1505.227982468619</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N37" t="n">
-        <v>1348.401726605517</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O37" t="n">
-        <v>1114.295626111728</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>819.929907664552</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881904</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949744336</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
       </c>
       <c r="T37" t="n">
-        <v>164.4096660440817</v>
+        <v>164.4096660440508</v>
       </c>
       <c r="U37" t="n">
-        <v>332.7843563872864</v>
+        <v>332.7843563872555</v>
       </c>
       <c r="V37" t="n">
-        <v>453.3957492732324</v>
+        <v>453.3957492732014</v>
       </c>
       <c r="W37" t="n">
-        <v>547.0766675329098</v>
+        <v>547.0766675328789</v>
       </c>
       <c r="X37" t="n">
-        <v>619.8974585571034</v>
+        <v>619.8974585570725</v>
       </c>
       <c r="Y37" t="n">
-        <v>653.0967592361357</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="38">
@@ -7165,25 +7165,25 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K38" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L38" t="n">
-        <v>949.6332762537361</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M38" t="n">
-        <v>1592.143276253736</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N38" t="n">
-        <v>1651.83297330616</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O38" t="n">
-        <v>1812.963074689115</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P38" t="n">
-        <v>2009.555081027735</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>168.4528527561725</v>
+        <v>992.2829698086706</v>
       </c>
       <c r="C39" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424895</v>
       </c>
       <c r="D39" t="n">
-        <v>100.7381059448373</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E39" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600498</v>
       </c>
       <c r="F39" t="n">
-        <v>60.02261143999941</v>
+        <v>235.3678800076489</v>
       </c>
       <c r="G39" t="n">
-        <v>55.98259997866057</v>
+        <v>231.3278685463101</v>
       </c>
       <c r="H39" t="n">
         <v>51.92</v>
@@ -7271,25 +7271,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S39" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T39" t="n">
-        <v>1846.683151095642</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U39" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V39" t="n">
         <v>1348.024214018445</v>
       </c>
       <c r="W39" t="n">
-        <v>911.2836656246793</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X39" t="n">
-        <v>487.1798884071161</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y39" t="n">
-        <v>232.6513948231691</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="40">
@@ -7323,31 +7323,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.576154611905</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K40" t="n">
-        <v>1619.080700024183</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L40" t="n">
-        <v>1608.654647405794</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M40" t="n">
-        <v>1505.227982468627</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N40" t="n">
-        <v>1348.401726605524</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O40" t="n">
-        <v>1114.295626111735</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645594</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881978</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949745075</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7396,7 +7396,7 @@
         <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I41" t="n">
         <v>51.92</v>
@@ -7405,22 +7405,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L41" t="n">
-        <v>950.0896384907273</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M41" t="n">
-        <v>1592.599638490728</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N41" t="n">
-        <v>2235.109638490728</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O41" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P41" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1141.180125483445</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C42" t="n">
-        <v>776.43273917484</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D42" t="n">
-        <v>424.9805301872615</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E42" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600498</v>
       </c>
       <c r="F42" t="n">
-        <v>60.02261143999941</v>
+        <v>559.6103042500732</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866057</v>
+        <v>555.5702927887344</v>
       </c>
       <c r="H42" t="n">
-        <v>51.92</v>
+        <v>227.2652685676495</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C44" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D44" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E44" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F44" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G44" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H44" t="n">
         <v>51.92</v>
@@ -7642,49 +7642,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>307.5796384907274</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L44" t="n">
-        <v>950.0896384907273</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M44" t="n">
-        <v>1592.599638490728</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N44" t="n">
-        <v>2235.109638490728</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O44" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P44" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S44" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W44" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X44" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>668.0405455662465</v>
+        <v>588.6177696982188</v>
       </c>
       <c r="C45" t="n">
-        <v>627.5355835000654</v>
+        <v>223.8703833896134</v>
       </c>
       <c r="D45" t="n">
-        <v>600.3257987549113</v>
+        <v>196.6605986444593</v>
       </c>
       <c r="E45" t="n">
-        <v>578.4347914600501</v>
+        <v>174.769591349598</v>
       </c>
       <c r="F45" t="n">
-        <v>559.6103042500735</v>
+        <v>155.9451041396214</v>
       </c>
       <c r="G45" t="n">
-        <v>555.5702927887346</v>
+        <v>151.9050926782826</v>
       </c>
       <c r="H45" t="n">
-        <v>245.506782013369</v>
+        <v>147.842492699622</v>
       </c>
       <c r="I45" t="n">
         <v>51.92</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R45" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S45" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U45" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V45" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W45" t="n">
-        <v>1559.768514109528</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X45" t="n">
-        <v>1135.664736891965</v>
+        <v>1056.241961023937</v>
       </c>
       <c r="Y45" t="n">
-        <v>1056.481511875667</v>
+        <v>977.0587360076396</v>
       </c>
     </row>
     <row r="46">
@@ -7812,13 +7812,13 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O46" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q46" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R46" t="n">
         <v>82.79157247680381</v>
@@ -7970,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>183.3412755627362</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>846.2608914614127</v>
@@ -7979,7 +7979,7 @@
         <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>184.5002908654719</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -8201,7 +8201,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
@@ -8441,16 +8441,16 @@
         <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M8" t="n">
-        <v>655.6021670241489</v>
+        <v>772.4711016975157</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>911.3123136417682</v>
+        <v>699.241868512898</v>
       </c>
       <c r="N11" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L14" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M14" t="n">
-        <v>950.4344291498551</v>
+        <v>699.241868512898</v>
       </c>
       <c r="N14" t="n">
-        <v>409.6042294964216</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9155,13 +9155,13 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L17" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>409.6042294964216</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M23" t="n">
-        <v>318.9437086192779</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N23" t="n">
         <v>879.4920535472222</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>792.031789021288</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N26" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,16 +10097,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L29" t="n">
-        <v>159.4556686723377</v>
+        <v>378.150932086181</v>
       </c>
       <c r="M29" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N29" t="n">
         <v>230.4920535472222</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>341.6095732017122</v>
+        <v>361.7270524351312</v>
       </c>
       <c r="N32" t="n">
         <v>879.4920535472222</v>
@@ -10352,7 +10352,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,28 +10571,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M35" t="n">
-        <v>467.8533356222227</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
         <v>879.4920535472222</v>
       </c>
       <c r="O35" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.48346824708341</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M38" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N38" t="n">
-        <v>290.7846768324985</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,16 +11048,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L41" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>879.4920535472222</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,10 +11285,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>950.4344291498551</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8382458495976817</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8382458495976959</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -24362,13 +24362,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -24596,10 +24596,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -24842,13 +24842,13 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -25076,7 +25076,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8382458495976266</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495668459</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495595273</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -26027,16 +26027,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
         <v>0.8382458495974561</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26296,22 +26296,22 @@
         <v>1290840.84549301</v>
       </c>
       <c r="K2" t="n">
+        <v>1290840.845493009</v>
+      </c>
+      <c r="L2" t="n">
         <v>1290840.84549301</v>
       </c>
-      <c r="L2" t="n">
-        <v>1290840.845493009</v>
-      </c>
       <c r="M2" t="n">
-        <v>1290840.845493011</v>
+        <v>1290840.84549301</v>
       </c>
       <c r="N2" t="n">
-        <v>1290840.845493011</v>
+        <v>1290840.84549301</v>
       </c>
       <c r="O2" t="n">
         <v>1290840.84549301</v>
       </c>
       <c r="P2" t="n">
-        <v>1290840.845493009</v>
+        <v>1290840.84549301</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570963.5697337883</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634525</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259448</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216768</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497198</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589559</v>
+        <v>468216.2325286013</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604934</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>423708.1316741448</v>
+        <v>430209.4966071221</v>
       </c>
       <c r="C6" t="n">
-        <v>656815.0538616331</v>
+        <v>663316.4187946104</v>
       </c>
       <c r="D6" t="n">
-        <v>658826.7012774574</v>
+        <v>665328.0662104342</v>
       </c>
       <c r="E6" t="n">
-        <v>137407.3166968346</v>
+        <v>143870.3078271891</v>
       </c>
       <c r="F6" t="n">
-        <v>728643.3795150582</v>
+        <v>735106.3706454117</v>
       </c>
       <c r="G6" t="n">
-        <v>730331.7690367111</v>
+        <v>736794.7601670647</v>
       </c>
       <c r="H6" t="n">
-        <v>732022.5019466738</v>
+        <v>738485.4930770278</v>
       </c>
       <c r="I6" t="n">
-        <v>733715.5951472207</v>
+        <v>740178.5862775752</v>
       </c>
       <c r="J6" t="n">
-        <v>346963.0657621451</v>
+        <v>353426.0568924996</v>
       </c>
       <c r="K6" t="n">
-        <v>737108.9311409795</v>
+        <v>743571.9222713324</v>
       </c>
       <c r="L6" t="n">
-        <v>738809.2088633223</v>
+        <v>745272.1999936772</v>
       </c>
       <c r="M6" t="n">
-        <v>643711.916743291</v>
+        <v>650174.907873645</v>
       </c>
       <c r="N6" t="n">
-        <v>742217.0728340548</v>
+        <v>748680.0639644087</v>
       </c>
       <c r="O6" t="n">
-        <v>487124.6954325162</v>
+        <v>493587.6865628709</v>
       </c>
       <c r="P6" t="n">
-        <v>745634.8030840994</v>
+        <v>752097.7942144546</v>
       </c>
     </row>
   </sheetData>
@@ -26984,10 +26984,10 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27005,7 +27005,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27106,7 +27106,7 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27521,16 +27521,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>172.2069069440305</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27560,13 +27560,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>183.8400581130405</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27597,28 +27597,28 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>175.6474368353911</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>396.2015953708939</v>
@@ -27648,10 +27648,10 @@
         <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>353.7792367911192</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27752,16 +27752,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>29.00266036063437</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>210.6652859026075</v>
       </c>
       <c r="G6" t="n">
         <v>325.5201396486123</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27828,16 +27828,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
@@ -27855,7 +27855,7 @@
         <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L7" t="n">
         <v>396.2015953708939</v>
@@ -27882,13 +27882,13 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T7" t="n">
-        <v>314.5177301457479</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
@@ -27897,7 +27897,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>311.0696464334873</v>
       </c>
     </row>
     <row r="8">
@@ -27986,19 +27986,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>210.6652859026075</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.5201396486123</v>
@@ -28052,10 +28052,10 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>328.4192594451154</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="10">
@@ -28065,37 +28065,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>295.7112478557377</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J10" t="n">
-        <v>108.5505688998659</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28122,19 +28122,19 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.3057582470187</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28223,22 +28223,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E12" t="n">
         <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="H12" t="n">
         <v>321</v>
@@ -28289,10 +28289,10 @@
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28460,10 +28460,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
         <v>321</v>
@@ -28472,7 +28472,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28511,16 +28511,16 @@
         <v>321</v>
       </c>
       <c r="S15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="U15" t="n">
         <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>321</v>
@@ -28636,7 +28636,7 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I17" t="n">
         <v>96.76634561233286</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28697,25 +28697,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
       </c>
       <c r="H18" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="I18" t="n">
         <v>191.6509141932353</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>321</v>
@@ -28757,10 +28757,10 @@
         <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X18" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28918,7 +28918,7 @@
         <v>321</v>
       </c>
       <c r="W20" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="X20" t="n">
         <v>321</v>
@@ -28937,7 +28937,7 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -28949,7 +28949,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="H21" t="n">
         <v>321</v>
@@ -29110,7 +29110,7 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>96.76634561233286</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>321</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R24" t="n">
         <v>321</v>
@@ -29231,16 +29231,16 @@
         <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29465,7 +29465,7 @@
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>147.4081841180266</v>
       </c>
       <c r="V27" t="n">
         <v>321</v>
@@ -29474,7 +29474,7 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -29645,10 +29645,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
         <v>321</v>
@@ -29702,19 +29702,19 @@
         <v>321</v>
       </c>
       <c r="U30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31">
@@ -29821,10 +29821,10 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I32" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29885,10 +29885,10 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -29897,10 +29897,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>321</v>
+        <v>226.0367322273744</v>
       </c>
       <c r="H33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>191.6509141932353</v>
@@ -30122,10 +30122,10 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="D36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>321</v>
@@ -30140,7 +30140,7 @@
         <v>321</v>
       </c>
       <c r="I36" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,10 +30164,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>321</v>
+        <v>96.68764642060938</v>
       </c>
       <c r="S36" t="n">
         <v>321</v>
@@ -30182,10 +30182,10 @@
         <v>321</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y36" t="n">
         <v>321</v>
@@ -30252,7 +30252,7 @@
         <v>321</v>
       </c>
       <c r="T37" t="n">
-        <v>321.0000000000312</v>
+        <v>321</v>
       </c>
       <c r="U37" t="n">
         <v>321</v>
@@ -30365,16 +30365,16 @@
         <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
       </c>
       <c r="H39" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="I39" t="n">
         <v>191.6509141932353</v>
@@ -30407,7 +30407,7 @@
         <v>321</v>
       </c>
       <c r="S39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>321</v>
@@ -30416,16 +30416,16 @@
         <v>321</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40">
@@ -30459,7 +30459,7 @@
         <v>321</v>
       </c>
       <c r="J40" t="n">
-        <v>321.0000000000385</v>
+        <v>321</v>
       </c>
       <c r="K40" t="n">
         <v>321</v>
@@ -30532,10 +30532,10 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I41" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -30611,10 +30611,10 @@
         <v>321</v>
       </c>
       <c r="H42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>191.6509141932353</v>
+        <v>18.05909831126235</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30769,7 +30769,7 @@
         <v>321</v>
       </c>
       <c r="H44" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I44" t="n">
         <v>96.76634561233286</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30833,7 +30833,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>321</v>
@@ -30848,10 +30848,10 @@
         <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>18.05909831126206</v>
+        <v>321</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>96.68764642060955</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
@@ -34749,7 +34749,7 @@
         <v>52.1599296482412</v>
       </c>
       <c r="L2" t="n">
-        <v>248.0502805878618</v>
+        <v>64.70900502512562</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
@@ -34758,7 +34758,7 @@
         <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="P2" t="n">
         <v>58.67867865278593</v>
@@ -34883,28 +34883,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>155.1400615846995</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4.545391051338453</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34934,10 +34934,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>202.8308783035465</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824119</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L5" t="n">
         <v>248.0502805878618</v>
@@ -34992,7 +34992,7 @@
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35114,16 +35114,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
@@ -35141,7 +35141,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,13 +35168,13 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>105.2790652788345</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -35183,7 +35183,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>23.60429358402495</v>
       </c>
     </row>
     <row r="8">
@@ -35220,16 +35220,16 @@
         <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824119</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>183.3412755627362</v>
+        <v>300.210210236103</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,37 +35351,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>10.17502980018224</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>86.28578399838436</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>190.7613351330866</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K11" t="n">
+        <v>648.9999999999999</v>
+      </c>
+      <c r="L11" t="n">
         <v>649</v>
       </c>
-      <c r="L11" t="n">
-        <v>218.2342914572864</v>
-      </c>
       <c r="M11" t="n">
-        <v>609.8778844919133</v>
+        <v>397.807439363043</v>
       </c>
       <c r="N11" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
-        <v>649</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>649</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>397.807439363043</v>
       </c>
       <c r="N14" t="n">
-        <v>179.1121759491994</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -35843,7 +35843,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H16" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I16" t="n">
         <v>163.0214951995539</v>
@@ -35934,13 +35934,13 @@
         <v>649</v>
       </c>
       <c r="L17" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M17" t="n">
         <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>179.1121759491994</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -36080,7 +36080,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H19" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I19" t="n">
         <v>163.0214951995539</v>
@@ -36317,7 +36317,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H22" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I22" t="n">
         <v>163.0214951995539</v>
@@ -36408,10 +36408,10 @@
         <v>649</v>
       </c>
       <c r="L23" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M23" t="n">
-        <v>17.50927946942293</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N23" t="n">
         <v>649</v>
@@ -36423,7 +36423,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36639,25 +36639,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K26" t="n">
-        <v>175.9119195979899</v>
+        <v>434.7823270636903</v>
       </c>
       <c r="L26" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>490.597359871433</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P26" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q26" t="n">
         <v>592.3686050224903</v>
@@ -36876,16 +36876,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K29" t="n">
-        <v>649</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>377.6899601296241</v>
+        <v>596.3852235434674</v>
       </c>
       <c r="M29" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
         <v>175.9119195979899</v>
@@ -37122,7 +37122,7 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M32" t="n">
-        <v>40.17514405185721</v>
+        <v>60.29262328527617</v>
       </c>
       <c r="N32" t="n">
         <v>649</v>
@@ -37131,7 +37131,7 @@
         <v>162.757678164601</v>
       </c>
       <c r="P32" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
         <v>592.3686050224903</v>
@@ -37265,7 +37265,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H34" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I34" t="n">
         <v>163.0214951995539</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L35" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M35" t="n">
-        <v>166.4189064723678</v>
+        <v>649</v>
       </c>
       <c r="N35" t="n">
         <v>649</v>
       </c>
       <c r="O35" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P35" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>113.6259252970522</v>
+        <v>113.625925297021</v>
       </c>
       <c r="U37" t="n">
         <v>170.0754447911158</v>
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K38" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M38" t="n">
         <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>60.29262328527629</v>
+        <v>649</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37608,7 +37608,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>592.3686050224903</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>163.0214951995539</v>
       </c>
       <c r="J40" t="n">
-        <v>329.5882314919996</v>
+        <v>329.5882314919611</v>
       </c>
       <c r="K40" t="n">
         <v>104.5500458709881</v>
@@ -37827,16 +37827,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L41" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38064,10 +38064,10 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L44" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
         <v>649</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
